--- a/data/processed/for_analysis/datacenters_matched_tracts.xlsx
+++ b/data/processed/for_analysis/datacenters_matched_tracts.xlsx
@@ -1295,12 +1295,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>51153901418</t>
+          <t>51153901408</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9014.18</t>
+          <t>9014.08</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>901418</t>
+          <t>901408</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>51153901418</t>
+          <t>51153901408</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9014.18</t>
+          <t>9014.08</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>901418</t>
+          <t>901408</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>51153901418</t>
+          <t>51153901408</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9014.18</t>
+          <t>9014.08</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>901418</t>
+          <t>901408</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>51153901421</t>
+          <t>51153901410</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9014.21</t>
+          <t>9014.10</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>901421</t>
+          <t>901410</t>
         </is>
       </c>
     </row>
@@ -5300,12 +5300,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>51059490104</t>
+          <t>51059490103</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>4901.04</t>
+          <t>4901.03</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490103</t>
         </is>
       </c>
     </row>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>51059490104</t>
+          <t>51059490103</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>4901.04</t>
+          <t>4901.03</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490103</t>
         </is>
       </c>
     </row>
@@ -5813,12 +5813,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>51059490104</t>
+          <t>51059490103</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>4901.04</t>
+          <t>4901.03</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490103</t>
         </is>
       </c>
     </row>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>51059490104</t>
+          <t>51059490103</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>4901.04</t>
+          <t>4901.03</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490103</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>51059490104</t>
+          <t>51059490103</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>4901.04</t>
+          <t>4901.03</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490103</t>
         </is>
       </c>
     </row>
@@ -6310,12 +6310,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>51059490104</t>
+          <t>51059490103</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>4901.04</t>
+          <t>4901.03</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490103</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -7006,12 +7006,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -11274,12 +11274,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>51059460503</t>
+          <t>51059460502</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>4605.03</t>
+          <t>4605.02</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>460503</t>
+          <t>460502</t>
         </is>
       </c>
     </row>
@@ -11439,12 +11439,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>51059460503</t>
+          <t>51059460502</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>4605.03</t>
+          <t>4605.02</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>460503</t>
+          <t>460502</t>
         </is>
       </c>
     </row>
@@ -13895,12 +13895,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>51153901418</t>
+          <t>51153901408</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>9014.18</t>
+          <t>9014.08</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>901418</t>
+          <t>901408</t>
         </is>
       </c>
     </row>
@@ -14070,12 +14070,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>51153901418</t>
+          <t>51153901408</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>9014.18</t>
+          <t>9014.08</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>901418</t>
+          <t>901408</t>
         </is>
       </c>
     </row>
@@ -14245,12 +14245,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>51153901418</t>
+          <t>51153901408</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>9014.18</t>
+          <t>9014.08</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>901418</t>
+          <t>901408</t>
         </is>
       </c>
     </row>
@@ -15643,12 +15643,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>51153901420</t>
+          <t>51153901410</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>9014.20</t>
+          <t>9014.10</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>901420</t>
+          <t>901410</t>
         </is>
       </c>
     </row>
@@ -15818,12 +15818,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>51153901420</t>
+          <t>51153901410</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>9014.20</t>
+          <t>9014.10</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>901420</t>
+          <t>901410</t>
         </is>
       </c>
     </row>
@@ -16176,12 +16176,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -19370,12 +19370,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -19549,12 +19549,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -19728,12 +19728,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -19907,12 +19907,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>51107611901</t>
+          <t>51107611900</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>6119.01</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>611901</t>
+          <t>611900</t>
         </is>
       </c>
     </row>
@@ -20086,12 +20086,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>51107611901</t>
+          <t>51107611900</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>6119.01</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>611901</t>
+          <t>611900</t>
         </is>
       </c>
     </row>
@@ -20577,12 +20577,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>51153901418</t>
+          <t>51153901408</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>9014.18</t>
+          <t>9014.08</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>901418</t>
+          <t>901408</t>
         </is>
       </c>
     </row>
@@ -22498,12 +22498,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -22677,12 +22677,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -22856,12 +22856,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -23035,12 +23035,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -23055,7 +23055,7 @@
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -25143,12 +25143,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -25163,7 +25163,7 @@
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -25314,12 +25314,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -25493,12 +25493,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -25513,7 +25513,7 @@
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -28174,12 +28174,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -28194,7 +28194,7 @@
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -28353,12 +28353,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -29918,12 +29918,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -30097,12 +30097,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>51107611810</t>
+          <t>51107611806</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>6118.10</t>
+          <t>6118.06</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -30117,7 +30117,7 @@
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>611810</t>
+          <t>611806</t>
         </is>
       </c>
     </row>
@@ -30276,12 +30276,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>51107611810</t>
+          <t>51107611806</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>6118.10</t>
+          <t>6118.06</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -30296,7 +30296,7 @@
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>611810</t>
+          <t>611806</t>
         </is>
       </c>
     </row>
@@ -30451,12 +30451,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>51107611028</t>
+          <t>51107611024</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>6110.28</t>
+          <t>6110.24</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="AQ171" t="inlineStr">
         <is>
-          <t>611028</t>
+          <t>611024</t>
         </is>
       </c>
     </row>
@@ -30805,12 +30805,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -30825,7 +30825,7 @@
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -32404,12 +32404,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -32583,12 +32583,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -32762,12 +32762,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>51107611901</t>
+          <t>51107611900</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>6119.01</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>611901</t>
+          <t>611900</t>
         </is>
       </c>
     </row>
@@ -32941,12 +32941,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>51107611901</t>
+          <t>51107611900</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>6119.01</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -32961,7 +32961,7 @@
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>611901</t>
+          <t>611900</t>
         </is>
       </c>
     </row>
@@ -35023,12 +35023,12 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>51153901420</t>
+          <t>51153901410</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>9014.20</t>
+          <t>9014.10</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>901420</t>
+          <t>901410</t>
         </is>
       </c>
     </row>
@@ -35894,12 +35894,12 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -35914,7 +35914,7 @@
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -36065,12 +36065,12 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -36085,7 +36085,7 @@
       </c>
       <c r="AQ203" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -36236,12 +36236,12 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -36256,7 +36256,7 @@
       </c>
       <c r="AQ204" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -36405,12 +36405,12 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -36425,7 +36425,7 @@
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -38491,12 +38491,12 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -38511,7 +38511,7 @@
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -38845,12 +38845,12 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -40221,12 +40221,12 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -40241,7 +40241,7 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -40386,12 +40386,12 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>51107611901</t>
+          <t>51107611900</t>
         </is>
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>6119.01</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>611901</t>
+          <t>611900</t>
         </is>
       </c>
     </row>
@@ -40565,12 +40565,12 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -40585,7 +40585,7 @@
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -40744,12 +40744,12 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -43206,12 +43206,12 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
@@ -43226,7 +43226,7 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -44083,12 +44083,12 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>51059490104</t>
+          <t>51059490103</t>
         </is>
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>4901.04</t>
+          <t>4901.03</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
@@ -44103,7 +44103,7 @@
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490103</t>
         </is>
       </c>
     </row>
@@ -44248,12 +44248,12 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>51059490104</t>
+          <t>51059490103</t>
         </is>
       </c>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>4901.04</t>
+          <t>4901.03</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
@@ -44268,7 +44268,7 @@
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490103</t>
         </is>
       </c>
     </row>
@@ -44771,12 +44771,12 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>51153901421</t>
+          <t>51153901410</t>
         </is>
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>9014.21</t>
+          <t>9014.10</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
@@ -44791,7 +44791,7 @@
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>901421</t>
+          <t>901410</t>
         </is>
       </c>
     </row>
@@ -46165,12 +46165,12 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN261" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
@@ -46185,7 +46185,7 @@
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -46340,12 +46340,12 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>51107611702</t>
+          <t>51107611700</t>
         </is>
       </c>
       <c r="AN262" t="inlineStr">
         <is>
-          <t>6117.02</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
@@ -46360,7 +46360,7 @@
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
-          <t>611702</t>
+          <t>611700</t>
         </is>
       </c>
     </row>
@@ -47370,12 +47370,12 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>51153901421</t>
+          <t>51153901410</t>
         </is>
       </c>
       <c r="AN268" t="inlineStr">
         <is>
-          <t>9014.21</t>
+          <t>9014.10</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -47390,7 +47390,7 @@
       </c>
       <c r="AQ268" t="inlineStr">
         <is>
-          <t>901421</t>
+          <t>901410</t>
         </is>
       </c>
     </row>
@@ -48557,12 +48557,12 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>51107611028</t>
+          <t>51107611024</t>
         </is>
       </c>
       <c r="AN275" t="inlineStr">
         <is>
-          <t>6110.28</t>
+          <t>6110.24</t>
         </is>
       </c>
       <c r="AO275" t="inlineStr">
@@ -48577,7 +48577,7 @@
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
-          <t>611028</t>
+          <t>611024</t>
         </is>
       </c>
     </row>
@@ -48732,12 +48732,12 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>51107611028</t>
+          <t>51107611024</t>
         </is>
       </c>
       <c r="AN276" t="inlineStr">
         <is>
-          <t>6110.28</t>
+          <t>6110.24</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
@@ -48752,7 +48752,7 @@
       </c>
       <c r="AQ276" t="inlineStr">
         <is>
-          <t>611028</t>
+          <t>611024</t>
         </is>
       </c>
     </row>
@@ -48907,12 +48907,12 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>51107611028</t>
+          <t>51107611024</t>
         </is>
       </c>
       <c r="AN277" t="inlineStr">
         <is>
-          <t>6110.28</t>
+          <t>6110.24</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
@@ -48927,7 +48927,7 @@
       </c>
       <c r="AQ277" t="inlineStr">
         <is>
-          <t>611028</t>
+          <t>611024</t>
         </is>
       </c>
     </row>
@@ -49068,12 +49068,12 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>51107611810</t>
+          <t>51107611806</t>
         </is>
       </c>
       <c r="AN278" t="inlineStr">
         <is>
-          <t>6118.10</t>
+          <t>6118.06</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -49088,7 +49088,7 @@
       </c>
       <c r="AQ278" t="inlineStr">
         <is>
-          <t>611810</t>
+          <t>611806</t>
         </is>
       </c>
     </row>
@@ -49233,12 +49233,12 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>51107611810</t>
+          <t>51107611806</t>
         </is>
       </c>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>6118.10</t>
+          <t>6118.06</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
@@ -49253,7 +49253,7 @@
       </c>
       <c r="AQ279" t="inlineStr">
         <is>
-          <t>611810</t>
+          <t>611806</t>
         </is>
       </c>
     </row>
@@ -50102,12 +50102,12 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>51107611812</t>
+          <t>51107611801</t>
         </is>
       </c>
       <c r="AN284" t="inlineStr">
         <is>
-          <t>6118.12</t>
+          <t>6118.01</t>
         </is>
       </c>
       <c r="AO284" t="inlineStr">
@@ -50122,7 +50122,7 @@
       </c>
       <c r="AQ284" t="inlineStr">
         <is>
-          <t>611812</t>
+          <t>611801</t>
         </is>
       </c>
     </row>
@@ -50597,12 +50597,12 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>51059482505</t>
+          <t>51059482501</t>
         </is>
       </c>
       <c r="AN287" t="inlineStr">
         <is>
-          <t>4825.05</t>
+          <t>4825.01</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AQ287" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>482501</t>
         </is>
       </c>
     </row>
@@ -50762,12 +50762,12 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>51059482505</t>
+          <t>51059482501</t>
         </is>
       </c>
       <c r="AN288" t="inlineStr">
         <is>
-          <t>4825.05</t>
+          <t>4825.01</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -50782,7 +50782,7 @@
       </c>
       <c r="AQ288" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>482501</t>
         </is>
       </c>
     </row>
@@ -50927,12 +50927,12 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>51059482505</t>
+          <t>51059482501</t>
         </is>
       </c>
       <c r="AN289" t="inlineStr">
         <is>
-          <t>4825.05</t>
+          <t>4825.01</t>
         </is>
       </c>
       <c r="AO289" t="inlineStr">
@@ -50947,7 +50947,7 @@
       </c>
       <c r="AQ289" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>482501</t>
         </is>
       </c>
     </row>
@@ -51881,12 +51881,12 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>51061930306</t>
+          <t>51061930302</t>
         </is>
       </c>
       <c r="AN295" t="inlineStr">
         <is>
-          <t>9303.06</t>
+          <t>9303.02</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">
@@ -51901,7 +51901,7 @@
       </c>
       <c r="AQ295" t="inlineStr">
         <is>
-          <t>930306</t>
+          <t>930302</t>
         </is>
       </c>
     </row>
@@ -51992,12 +51992,12 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>51061930306</t>
+          <t>51061930302</t>
         </is>
       </c>
       <c r="AN296" t="inlineStr">
         <is>
-          <t>9303.06</t>
+          <t>9303.02</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
@@ -52012,7 +52012,7 @@
       </c>
       <c r="AQ296" t="inlineStr">
         <is>
-          <t>930306</t>
+          <t>930302</t>
         </is>
       </c>
     </row>
@@ -52336,12 +52336,12 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>51107611028</t>
+          <t>51107611024</t>
         </is>
       </c>
       <c r="AN298" t="inlineStr">
         <is>
-          <t>6110.28</t>
+          <t>6110.24</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">
@@ -52356,7 +52356,7 @@
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>611028</t>
+          <t>611024</t>
         </is>
       </c>
     </row>
@@ -52511,12 +52511,12 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>51107611028</t>
+          <t>51107611024</t>
         </is>
       </c>
       <c r="AN299" t="inlineStr">
         <is>
-          <t>6110.28</t>
+          <t>6110.24</t>
         </is>
       </c>
       <c r="AO299" t="inlineStr">
@@ -52531,7 +52531,7 @@
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>611028</t>
+          <t>611024</t>
         </is>
       </c>
     </row>
@@ -52676,12 +52676,12 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>51059482505</t>
+          <t>51059482501</t>
         </is>
       </c>
       <c r="AN300" t="inlineStr">
         <is>
-          <t>4825.05</t>
+          <t>4825.01</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
@@ -52696,7 +52696,7 @@
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>482501</t>
         </is>
       </c>
     </row>
@@ -52835,12 +52835,12 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>51059482505</t>
+          <t>51059482501</t>
         </is>
       </c>
       <c r="AN301" t="inlineStr">
         <is>
-          <t>4825.05</t>
+          <t>4825.01</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
@@ -52855,7 +52855,7 @@
       </c>
       <c r="AQ301" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>482501</t>
         </is>
       </c>
     </row>
@@ -54344,12 +54344,12 @@
       </c>
       <c r="AM310" t="inlineStr">
         <is>
-          <t>51153901421</t>
+          <t>51153901410</t>
         </is>
       </c>
       <c r="AN310" t="inlineStr">
         <is>
-          <t>9014.21</t>
+          <t>9014.10</t>
         </is>
       </c>
       <c r="AO310" t="inlineStr">
@@ -54364,7 +54364,7 @@
       </c>
       <c r="AQ310" t="inlineStr">
         <is>
-          <t>901421</t>
+          <t>901410</t>
         </is>
       </c>
     </row>
@@ -54688,12 +54688,12 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>51107611810</t>
+          <t>51107611806</t>
         </is>
       </c>
       <c r="AN312" t="inlineStr">
         <is>
-          <t>6118.10</t>
+          <t>6118.06</t>
         </is>
       </c>
       <c r="AO312" t="inlineStr">
@@ -54708,7 +54708,7 @@
       </c>
       <c r="AQ312" t="inlineStr">
         <is>
-          <t>611810</t>
+          <t>611806</t>
         </is>
       </c>
     </row>
